--- a/data/acme_robotics/hr_roster_acme.xlsx
+++ b/data/acme_robotics/hr_roster_acme.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Notes (DRAFT)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Notes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -602,7 +602,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>STATUS: DRAFT - authored Day 2 (D2-M6); finalized Day 3 (D3-M7).</t>
+          <t>STATUS: finalized Day 3 (D3-M7); authored Day 2 (D2-M6).</t>
         </is>
       </c>
     </row>

--- a/data/acme_robotics/hr_roster_acme.xlsx
+++ b/data/acme_robotics/hr_roster_acme.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Roster" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Notes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roster" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
